--- a/build/report-suite/reconciliation-2026-07-28/Report-Suite_Spec-Reconciliation_ChangeList_2026-07-28.xlsx
+++ b/build/report-suite/reconciliation-2026-07-28/Report-Suite_Spec-Reconciliation_ChangeList_2026-07-28.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Change list" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Blocked on Chris spec update" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Applied locally - to push" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +35,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -54,7 +54,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00A9D08E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,6 +123,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -495,21 +511,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Report Suite - spec-relevance reconciliation change list (2026-07-28)</t>
+          <t>Report Suite - spec-relevance reconciliation change list (2026-07-28, video-promotion update)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>515 cases total. 2 edited now (green). The rest need a decision or await Chris's spec update / a live-build check - listed below. All other cases are clean (no change needed now). NO TestRail writes this pass.</t>
+          <t>USER RULING 2026-07-28: Chris Ward's kickoff video is authentic + authoritative product intent and NEWER than the specs (last updated 2026-07-21) - the video overrides the spec where they conflict (last-update-wins). The previously 'blocked on Chris' rows are now APPLIED-LOCALLY: 14 rows edited/authored in the local case source + 1 retire-proposed. 516 cases total (515 in TestRail + 1 new). NO TestRail writes - this list is the approval gate for the push.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Legend: APPLIED-NOW = edited locally this pass (firmly confirmed). PENDING-CHRIS = video intent the current spec still contradicts - not edited, awaiting Chris's spec update. OPEN-DECISION = not settled on the call. LIVE-VIU-PENDING = needs the live QA build to confirm (no QA branch yet).</t>
+          <t>Legend: APPLIED-NOW = edited locally in the first pass (Chris's written answer). APPLIED-LOCALLY = video-authoritative / latest-info edit applied to the local case source (user ruling 2026-07-28) - awaiting TestRail push authorization. RETIRE-PROPOSED = proposed for deletion, NOT deleted - awaiting authorization. NO-CHANGE-CONFIRMED = latest info confirms the cases already match. OPEN-DECISION = not settled. LIVE-VIU-PENDING = needs the live QA build to confirm (no QA branch yet). Backups of every touched case: build/report-suite/video-promotion-backup-2026-07-28/ (recover if Chris never ratifies). Spec-watch deadline 2026-08-04: build/report-suite/SPEC-WATCH-2026-07-28.md.</t>
         </is>
       </c>
     </row>
@@ -583,7 +599,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>DONE THIS PASS. Reworded so pressing the Esc key does NOT close the 'deactivate a sales rep' confirm pop-up - only the Cancel button and the X icon close it (matches Chris's answer and the app's house rule that pop-ups do not close on Esc). Long title shortened to fit. Still to be confirmed live on the QA branch.</t>
+          <t>DONE (first pass). Reworded so pressing the Esc key does NOT close the 'deactivate a sales rep' confirm pop-up - only the Cancel button and the X icon close it (matches Chris's answer and the app's house rule that pop-ups do not close on Esc). Long title shortened to fit. Still to be confirmed live on the QA branch.</t>
         </is>
       </c>
     </row>
@@ -620,7 +636,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>DONE THIS PASS. Small consistency fix: made clear the Esc key never closes this dialog at any time (aligns with the case above). Overlong title shortened. Confirm live.</t>
+          <t>DONE (first pass). Small consistency fix: made clear the Esc key never closes this dialog at any time (aligns with the case above). Overlong title shortened. Confirm live.</t>
         </is>
       </c>
     </row>
@@ -652,12 +668,12 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>If Chris ratifies it, change the asset label to use the SERIAL NUMBER (bin number) as the identifier instead of Unit -&gt; plate -&gt; VIN. NOT changed yet: the current written spec (S8-R8 '· Unit {unit}') still uses the unit number, and Chris said he will 'double-check the spec' first. Also touches SBC-LBL-02 C30135, SBC-LBL-03 C30136, SBC-LBL-04 C30137.</t>
+          <t>DONE LOCALLY. The asset label now uses the SERIAL NUMBER as the identifier (video: 'the holy grail... is the serial number, or in some cases the bin number'), replacing the spec's Unit -&gt; plate -&gt; VIN chain (S8-R8 OVERRIDDEN). What stands in when the serial is missing is flagged 'confirmed in the build' - not invented. SBC-LBL-02 C30135 / SBC-LBL-03 C30136 / SBC-LBL-04 C30137 got notes/refs updates only (their own rules are not overridden). Needs an authorized update_case push, then live confirmation.</t>
         </is>
       </c>
     </row>
@@ -689,12 +705,12 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Same serial-number change for the Work In Progress Asset cell (currently the unit number over the VIN, per spec S4-R7). NOT changed yet - awaiting Chris's spec update. Also touches WIP-FLT-03 C30500, WIP-SORT-03 C30485, WIP-EXP-07 C30516.</t>
+          <t>DONE LOCALLY. The Work In Progress Asset cell's bold first line is now the SERIAL NUMBER (spec S4-R7 unit number OVERRIDDEN); the missing-serial placeholder text is flagged 'confirmed in the build'. Same serial-number change applied to WIP-FLT-03 C30500 (asset filter options + type-ahead), WIP-SORT-03 C30485 (Asset sort key), and a tester caveat added to WIP-EXP-07 C30516 (export header 'Unit' - record what it shows, do not file). Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -726,29 +742,29 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>If Chris cuts Print from the spec, remove the 'Print' item from the report's overflow (three-dot) menu. NOT changed yet: the current spec (Story 16) still includes Print; Chris said 'this should not exist... I'm going to make sure that's cut out of the spec.'</t>
+          <t>DONE LOCALLY. The overflow menu expectation is now 'Download (CSV)', 'Download (PDF)' with NO 'Print' item (video: 'print here, this should not exist. I'm going to make sure that's cut out of the spec' - spec Story 16 + S14-R1 'Print' third item OVERRIDDEN). Needs an authorized push.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>SBC-EXP-13</t>
+          <t>SBC-EXP-14</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>C30171</t>
+          <t>C30172</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30171</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30172</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -763,23 +779,31 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Retire the SBC Print-behavior case once Print is cut from the spec. NOT changed yet. Print is also referenced in the empty-state export case SBC-EXP-15 C30173.</t>
+          <t>DONE LOCALLY. The Print leg was removed from the 10,000-row-cap export negative (CSV + PDF legs kept); overlong title shortened. CORRECTION to the earlier list: the third Print reference lives HERE (SBC-EXP-14 C30172), not in SBC-EXP-15 C30173 (which has no Print reference and is untouched). Needs an authorized push.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>(new - to author)</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr"/>
-      <c r="C12" s="3" t="inlineStr"/>
+          <t>SBC-EXP-13</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>C30171</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30171</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>SBC</t>
@@ -787,36 +811,28 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Video P21 - add compressed download</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>PENDING-CHRIS</t>
+          <t>Video P25 - remove SBC Print</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>RETIRE-PROPOSED</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Chris agreed live to ADD a compressed/summary download to Sales By Customer, alongside the existing expanded (nested) download - like the other reports' Summary/Expanded split. NOT authored yet: the current spec has only the single flat export. Author a new export case once the spec adds it.</t>
+          <t>RETIRE PROPOSED - this case's ONLY purpose is the Print behavior and Print is removed from Sales By Customer. NOT deleted: it stays in TestRail (C30171) and in the import until you authorize delete_case (Rule 6). Marked Retire-Proposed locally; body left as authored for the record.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>SBC-LOC-03</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>C30111</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30111</t>
-        </is>
-      </c>
+          <t>SBC-EXP-16</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>SBC</t>
@@ -824,54 +840,54 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Video P10 - per-row location label</t>
+          <t>Video P21 - add compressed download</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>When 'All locations' is selected, add a per-row (or per-section) location label so a user can tell which shop each row belongs to. NOT added yet on the five non-WIP reports; add once the spec calls for it. Work In Progress already has a Location column. Also affects SBR-LOC-03 C30215, PV-FILT-10 C30337, TU-LOC-01 C30442, IV-LOC-01 C30574 - likely a new case per report.</t>
+          <t>DONE LOCALLY - NEW CASE AUTHORED (new - no C-ID yet). The download menu also offers a compressed (summary) version of the report alongside the expanded (nested) one (Parth's suggestion, Chris: 'That's actually a good callout. Let's, let's add that' + 'we're gonna have to add to SVC... the CompressedView'). Menu wording + file shape flagged 'confirmed in the build'. Needs an authorized add_case, then live confirmation.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>PV-FILT-01</t>
+          <t>SBC-LOC-03</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>C30328</t>
+          <t>C30111</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30111</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Video P31 - Catalogue rename</t>
+          <t>Video P10 - per-row location label</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>If Chris renames/truncates 'Catalogue' (it means special-order parts never stocked), update the Type filter option, the Type column value, and the tooltips to the new label. NOT changed yet - the rename is not decided and the current spec still says 'Catalogue'. Also touches PV-FILT-09 C30336, PV-ROW-05 C30345, PV-EXP-08 C30382.</t>
+          <t>DONE LOCALLY. Added the expectation that with 'All locations' active each row identifies WHICH location it belongs to (video: 'how do I know which is for shop A and which is for shop B?... we should probably add that in there'). The exact label/control is flagged 'confirmed in the build' - the video names none. Same add applied to SBR-LOC-03 C30215, PV-FILT-10 C30337, TU-LOC-01 C30442 (worded for TU's pooled rows), IV-LOC-01 C30574. Work In Progress already has a Location column - no WIP edit. Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -903,12 +919,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Chris's intent: HIDE the Location filter when a user can access only one location, SHOW it when they can access two or more. This case currently says the OPPOSITE (a one-location user STILL sees the filter, spec S21-N1) straight from the current spec. Do NOT change until Chris updates the spec - the written spec directly contradicts the video here. Ties to the Q2 permission question.</t>
+          <t>DONE LOCALLY - expectation FLIPPED. A user with permission to only ONE location does NOT see the Location filter at all; with two or more permitted locations the filter shows (video: 'the filter's just gone... if you had QA testing and QB location, then of course you'd see the filter'). Overrides spec S21-N1 ('a single-location user STILL SEES the filter'). Ties to the Q2 permission question. Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -940,12 +956,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Same location-filter hide-when-one-location change. NOT changed - the current spec (S9-N1) says a one-location user still sees the filter.</t>
+          <t>DONE LOCALLY - same flip (overrides spec S9-N1). Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -977,12 +993,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Same location-filter hide-when-one-location change. NOT changed - the current spec (S7-N1) says a one-location user still sees the filter.</t>
+          <t>DONE LOCALLY - same flip (overrides spec S7-N1). Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -1014,226 +1030,292 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Same location-filter hide-when-one-location change. NOT changed - the current spec (S2-E4) says a one-location user still sees the filter.</t>
+          <t>DONE LOCALLY - same flip (overrides spec S2-E4). Needs an authorized push.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>WIP-FLT-03</t>
+          <t>TU-NAV-01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>C30500</t>
+          <t>C30392</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30500</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30392</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>WIP</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Video P12 - asset dropdown behavior</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>OPEN-DECISION</t>
+          <t>Video P3 - move TU down in nav (additive, not interruptive)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Undecided on the call: the Asset dropdown stays open while you pick several (Chris) vs matching the native reports that close on each pick, plus a toggle (Stefan). Do not pass/fail on this until decided; confirm the final behavior live. Not changed.</t>
+          <t>DONE LOCALLY. Added the expectation that the Technician Utilization entry sits BELOW the previously existing report links (video: 'technician utilization is actually in a really bad spot right now. So, we want to move these down below what's already there'). The Performance-group expectation is kept. PV-NAV-01 C30322 + IV-NAV-01 C30534 already expect the new 'Parts' nav section (video P2) - verified, no edit needed. Needs an authorized push + live placement check.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>IV-PERS-01</t>
+          <t>PV-FILT-01</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>C30579</t>
+          <t>C30328</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30579</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30328</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>Video P18 / P36 - column-selector scope</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>OPEN-DECISION</t>
+          <t>Video P31 - Catalogue rename (latest info: leaning to rename)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Column-selector scope was left open across the suite (Chris vetoed one on Technician Utilization, 'not married to it'). Inventory Value currently HAS a column selector per the spec (S8-R1). Confirm with Chris whether Inventory Value keeps its selector. Not changed.</t>
+          <t>DONE LOCALLY per LATEST INFO (correct at VIU later). The Type filter's third option is now worded by MEANING - special-order catalog parts never put into stock - with the exact on-screen label flagged 'confirmed in the build' (video: 'maybe we do rename it... you're absolutely right' + 'we'll have to truncate that down'; both possible labels noted in the case note - 'Catalogue' per spec, or a short special-order-parts name, not invented). Same treatment on PV-FILT-09 C30336 and PV-ROW-05 C30345; PV-EXP-08 C30382 notes-only. Needs an authorized push.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>PV-API-01</t>
+          <t>WIP-FLT-03</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>C30388</t>
+          <t>C30500</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30500</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>WIP</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Video P30 - pagination vs infinite-scroll</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>OPEN-DECISION</t>
+          <t>Video P12 - asset dropdown style (latest info: match native + toggle)</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Chris wants to revisit forced pagination vs infinite-scroll / lazy-load for large part lists. The behavior may change; treat as a performance caveat and confirm live. Not changed. Also PV-API-02 C30389.</t>
+          <t>DONE LOCALLY per LATEST INFO. Latest information = match the native ShopView multi-select style plus a possible toggle (Stefan proposed, Chris agreed: 'let's please do this, happy to update the spec'). Verified NO case asserts the stay-open behavior - nothing to flip; this case's note now records the native+toggle expectation with the exact interaction = confirm live. (Its serial-number wording was also updated under P24 above.)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>(no case - TU)</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr"/>
+          <t>PV-API-01</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>C30388</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30388</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Video P18 - TU column selector</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>OPEN-DECISION</t>
+          <t>Video P30 - pagination (latest info: pagination on every page)</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>Chris vetoed a column selector on Technician Utilization but is 'not married to it.' Our TU cases correctly have none, matching the spec. No case to change now; if Chris later adds one, author cases then.</t>
+          <t>DONE LOCALLY per LATEST INFO. Stefan (definitive): 'we are definitely having pagination on every page'. Verified NO case asserts infinite-scroll or all-rows-at-once; the pagination cases already expect server pagination. PV-API-01 + PV-API-02 C30389 notes now flag the pagination-behavior details (page size, control style) as confirm-live; Chris's infinite-scroll revisit stays a later product question.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>WIP-CALC-08</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>C30481</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30481</t>
-        </is>
-      </c>
+          <t>(no case - TU)</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>WIP</t>
+          <t>TU</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Video P14 vs spec S4-R23 - labor-delta basis</t>
+          <t>Video P18 - TU column selector (latest info: veto stands)</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>LIVE-VIU-PENDING</t>
+          <t>NO-CHANGE-CONFIRMED</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Video P14 says the labor delta = clocked/tech hours vs INVOICED hours; the WIP spec (S4-R23) uses QUOTED (estimate) hours minus worked hours because WIP is a pre-invoice report. The case matches the SPEC (quoted-basis) and is NOT changed. Confirm live which basis actually ships. Do NOT conflate with Sales By Customer / Sales By Representative, which correctly use invoiced-minus-worked (SBC-CALC-03 C30151, SBR-CALC-02 C30230).</t>
+          <t>CONFIRMED NO-OP per LATEST INFO: Chris's veto stands and the spec agrees (no TU column-selector story). Verified no TU column-selector case exists - cases already match. If Chris later adds one, author cases then.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TU-NAV-01</t>
+          <t>IV-PERS-01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>C30392</t>
+          <t>C30579</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30579</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>TU</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Video P3 - move TU down in nav</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
+          <t>Video P18 / P36 - column-selector scope</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>OPEN-DECISION</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Column-selector scope was left open across the suite (Chris vetoed one on Technician Utilization, 'not married to it'). Inventory Value currently HAS a column selector per the spec (S8-R1). Confirm with Chris whether Inventory Value keeps its selector. Not changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>(follow-up - SBC/WIP)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>SBC/WIP</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Video P33 - hide location filter when &lt;=1 location</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>OPEN-DECISION</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>FOLLOW-UP flagged for completeness: SBC and Work In Progress have NO single-location filter case at all (their specs never had the 'still sees the filter' rule), so nothing on those two reports asserts the old behavior. Decide whether each needs a NEW hidden-filter case - not authored this pass (outside the promotion's scope).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>WIP-CALC-08</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>C30481</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30481</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Video P14 vs spec S4-R23 - labor-delta basis</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>LIVE-VIU-PENDING</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Video: Technician Utilization is in a bad nav spot and must move toward the bottom (additive, not interruptive). The spec says the order among the six reports does not matter, so no wording change; confirm the final nav placement live. Not changed.</t>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Video P14 says the labor delta = clocked/tech hours vs INVOICED hours; the WIP spec (S4-R23) uses QUOTED (estimate) hours minus worked hours because WIP is a pre-invoice report. The case matches the SPEC (quoted-basis) and is NOT changed - the video discusses the delta generally and does not explicitly override WIP's pre-invoice basis, so this stays a live-check, not a promotion. Confirm live which basis actually ships. Do NOT conflate with Sales By Customer / Sales By Representative, which correctly use invoiced-minus-worked (SBC-CALC-03 C30151, SBR-CALC-02 C30230).</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1263,14 +1345,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Report Suite - items blocked on Chris Ward's spec update (PENDING-CHRIS)</t>
+          <t>Report Suite - edits applied LOCALLY (video-authoritative), awaiting TestRail push authorization</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>These are firm video-intent items where the CURRENT written spec still says otherwise. Per the process, we do NOT rewrite cases to un-ratified verbal intent - each waits for Chris to update the Confluence spec, then we edit + live-VIU.</t>
+          <t>Every row below is already edited/authored in build/report-suite/cases/ (audit log video-promotion-edit-log-2026-07-28.md, with the driving video quote + the overridden spec wording per case). NOTHING is pushed: the push needs your explicit permission (update_case for the edits, add_case for SBC-EXP-16, delete_case for the retire-proposed row). After the push: live VIU on the QA branch.</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1421,12 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>If Chris ratifies it, change the asset label to use the SERIAL NUMBER (bin number) as the identifier instead of Unit -&gt; plate -&gt; VIN. NOT changed yet: the current written spec (S8-R8 '· Unit {unit}') still uses the unit number, and Chris said he will 'double-check the spec' first. Also touches SBC-LBL-02 C30135, SBC-LBL-03 C30136, SBC-LBL-04 C30137.</t>
+          <t>DONE LOCALLY. The asset label now uses the SERIAL NUMBER as the identifier (video: 'the holy grail... is the serial number, or in some cases the bin number'), replacing the spec's Unit -&gt; plate -&gt; VIN chain (S8-R8 OVERRIDDEN). What stands in when the serial is missing is flagged 'confirmed in the build' - not invented. SBC-LBL-02 C30135 / SBC-LBL-03 C30136 / SBC-LBL-04 C30137 got notes/refs updates only (their own rules are not overridden). Needs an authorized update_case push, then live confirmation.</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1458,12 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Same serial-number change for the Work In Progress Asset cell (currently the unit number over the VIN, per spec S4-R7). NOT changed yet - awaiting Chris's spec update. Also touches WIP-FLT-03 C30500, WIP-SORT-03 C30485, WIP-EXP-07 C30516.</t>
+          <t>DONE LOCALLY. The Work In Progress Asset cell's bold first line is now the SERIAL NUMBER (spec S4-R7 unit number OVERRIDDEN); the missing-serial placeholder text is flagged 'confirmed in the build'. Same serial-number change applied to WIP-FLT-03 C30500 (asset filter options + type-ahead), WIP-SORT-03 C30485 (Asset sort key), and a tester caveat added to WIP-EXP-07 C30516 (export header 'Unit' - record what it shows, do not file). Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -1413,29 +1495,29 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>If Chris cuts Print from the spec, remove the 'Print' item from the report's overflow (three-dot) menu. NOT changed yet: the current spec (Story 16) still includes Print; Chris said 'this should not exist... I'm going to make sure that's cut out of the spec.'</t>
+          <t>DONE LOCALLY. The overflow menu expectation is now 'Download (CSV)', 'Download (PDF)' with NO 'Print' item (video: 'print here, this should not exist. I'm going to make sure that's cut out of the spec' - spec Story 16 + S14-R1 'Print' third item OVERRIDDEN). Needs an authorized push.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>SBC-EXP-13</t>
+          <t>SBC-EXP-14</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>C30171</t>
+          <t>C30172</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30171</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30172</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1450,23 +1532,31 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Retire the SBC Print-behavior case once Print is cut from the spec. NOT changed yet. Print is also referenced in the empty-state export case SBC-EXP-15 C30173.</t>
+          <t>DONE LOCALLY. The Print leg was removed from the 10,000-row-cap export negative (CSV + PDF legs kept); overlong title shortened. CORRECTION to the earlier list: the third Print reference lives HERE (SBC-EXP-14 C30172), not in SBC-EXP-15 C30173 (which has no Print reference and is untouched). Needs an authorized push.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>(new - to author)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr"/>
+          <t>SBC-EXP-13</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>C30171</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30171</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>SBC</t>
@@ -1474,36 +1564,28 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Video P21 - add compressed download</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>PENDING-CHRIS</t>
+          <t>Video P25 - remove SBC Print</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>RETIRE-PROPOSED</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Chris agreed live to ADD a compressed/summary download to Sales By Customer, alongside the existing expanded (nested) download - like the other reports' Summary/Expanded split. NOT authored yet: the current spec has only the single flat export. Author a new export case once the spec adds it.</t>
+          <t>RETIRE PROPOSED - this case's ONLY purpose is the Print behavior and Print is removed from Sales By Customer. NOT deleted: it stays in TestRail (C30171) and in the import until you authorize delete_case (Rule 6). Marked Retire-Proposed locally; body left as authored for the record.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>SBC-LOC-03</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>C30111</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30111</t>
-        </is>
-      </c>
+          <t>SBC-EXP-16</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>SBC</t>
@@ -1511,54 +1593,54 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Video P10 - per-row location label</t>
+          <t>Video P21 - add compressed download</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>When 'All locations' is selected, add a per-row (or per-section) location label so a user can tell which shop each row belongs to. NOT added yet on the five non-WIP reports; add once the spec calls for it. Work In Progress already has a Location column. Also affects SBR-LOC-03 C30215, PV-FILT-10 C30337, TU-LOC-01 C30442, IV-LOC-01 C30574 - likely a new case per report.</t>
+          <t>DONE LOCALLY - NEW CASE AUTHORED (new - no C-ID yet). The download menu also offers a compressed (summary) version of the report alongside the expanded (nested) one (Parth's suggestion, Chris: 'That's actually a good callout. Let's, let's add that' + 'we're gonna have to add to SVC... the CompressedView'). Menu wording + file shape flagged 'confirmed in the build'. Needs an authorized add_case, then live confirmation.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>PV-FILT-01</t>
+          <t>SBC-LOC-03</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>C30328</t>
+          <t>C30111</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30111</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Video P31 - Catalogue rename</t>
+          <t>Video P10 - per-row location label</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>If Chris renames/truncates 'Catalogue' (it means special-order parts never stocked), update the Type filter option, the Type column value, and the tooltips to the new label. NOT changed yet - the rename is not decided and the current spec still says 'Catalogue'. Also touches PV-FILT-09 C30336, PV-ROW-05 C30345, PV-EXP-08 C30382.</t>
+          <t>DONE LOCALLY. Added the expectation that with 'All locations' active each row identifies WHICH location it belongs to (video: 'how do I know which is for shop A and which is for shop B?... we should probably add that in there'). The exact label/control is flagged 'confirmed in the build' - the video names none. Same add applied to SBR-LOC-03 C30215, PV-FILT-10 C30337, TU-LOC-01 C30442 (worded for TU's pooled rows), IV-LOC-01 C30574. Work In Progress already has a Location column - no WIP edit. Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1672,12 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Chris's intent: HIDE the Location filter when a user can access only one location, SHOW it when they can access two or more. This case currently says the OPPOSITE (a one-location user STILL sees the filter, spec S21-N1) straight from the current spec. Do NOT change until Chris updates the spec - the written spec directly contradicts the video here. Ties to the Q2 permission question.</t>
+          <t>DONE LOCALLY - expectation FLIPPED. A user with permission to only ONE location does NOT see the Location filter at all; with two or more permitted locations the filter shows (video: 'the filter's just gone... if you had QA testing and QB location, then of course you'd see the filter'). Overrides spec S21-N1 ('a single-location user STILL SEES the filter'). Ties to the Q2 permission question. Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1709,12 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Same location-filter hide-when-one-location change. NOT changed - the current spec (S9-N1) says a one-location user still sees the filter.</t>
+          <t>DONE LOCALLY - same flip (overrides spec S9-N1). Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1746,12 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Same location-filter hide-when-one-location change. NOT changed - the current spec (S7-N1) says a one-location user still sees the filter.</t>
+          <t>DONE LOCALLY - same flip (overrides spec S7-N1). Needs an authorized push.</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1783,160 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>PENDING-CHRIS</t>
+          <t>APPLIED-LOCALLY</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Same location-filter hide-when-one-location change. NOT changed - the current spec (S2-E4) says a one-location user still sees the filter.</t>
+          <t>DONE LOCALLY - same flip (overrides spec S2-E4). Needs an authorized push.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TU-NAV-01</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>C30392</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30392</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>TU</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Video P3 - move TU down in nav (additive, not interruptive)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>DONE LOCALLY. Added the expectation that the Technician Utilization entry sits BELOW the previously existing report links (video: 'technician utilization is actually in a really bad spot right now. So, we want to move these down below what's already there'). The Performance-group expectation is kept. PV-NAV-01 C30322 + IV-NAV-01 C30534 already expect the new 'Parts' nav section (video P2) - verified, no edit needed. Needs an authorized push + live placement check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>PV-FILT-01</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>C30328</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30328</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Video P31 - Catalogue rename (latest info: leaning to rename)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>DONE LOCALLY per LATEST INFO (correct at VIU later). The Type filter's third option is now worded by MEANING - special-order catalog parts never put into stock - with the exact on-screen label flagged 'confirmed in the build' (video: 'maybe we do rename it... you're absolutely right' + 'we'll have to truncate that down'; both possible labels noted in the case note - 'Catalogue' per spec, or a short special-order-parts name, not invented). Same treatment on PV-FILT-09 C30336 and PV-ROW-05 C30345; PV-EXP-08 C30382 notes-only. Needs an authorized push.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>WIP-FLT-03</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>C30500</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30500</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>WIP</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Video P12 - asset dropdown style (latest info: match native + toggle)</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>DONE LOCALLY per LATEST INFO. Latest information = match the native ShopView multi-select style plus a possible toggle (Stefan proposed, Chris agreed: 'let's please do this, happy to update the spec'). Verified NO case asserts the stay-open behavior - nothing to flip; this case's note now records the native+toggle expectation with the exact interaction = confirm live. (Its serial-number wording was also updated under P24 above.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>PV-API-01</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>C30388</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30388</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Video P30 - pagination (latest info: pagination on every page)</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>APPLIED-LOCALLY</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>DONE LOCALLY per LATEST INFO. Stefan (definitive): 'we are definitely having pagination on every page'. Verified NO case asserts infinite-scroll or all-rows-at-once; the pagination cases already expect server pagination. PV-API-01 + PV-API-02 C30389 notes now flag the pagination-behavior details (page size, control style) as confirm-live; Chris's infinite-scroll revisit stays a later product question.</t>
         </is>
       </c>
     </row>
